--- a/docs/perechen-otchetov/obrazcy/ФО-18.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-18.xlsx
@@ -2031,7 +2031,7 @@
       <c r="N45" s="26" t="n"/>
       <c r="O45" s="23" t="inlineStr">
         <is>
-          <t>задание «Довнести страховой полис в дело» от 05.08.2026, срок 20.09.2026, исполнитель Токтогулова Г. А.</t>
+          <t>задание «Истребовать страховой полис у залогодателя» от 05.08.2026, срок 20.09.2026 (продлён 18.08.2026), исполнитель Токтогулова Г. А.</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="75" customHeight="1">
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="31" t="inlineStr">
         <is>
           <t>2.</t>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="B40" s="32" t="inlineStr">
         <is>
-          <t>КЗ-20 ОсОО «Каракол-Сервис» (куратор Токтогулова Г. А.): нет страхового полиса на нежилое помещение по договору залога № 25-3/014-З1 от 05.03.2025; открыто задание «Довнести страховой полис в дело» от 05.08.2026, срок 20.09.2026 — как в ФО-20, ФО-67, ФО-68. Отчёт об оценке от 10.03.2026 действует до 10.03.2027 (дата оценки — как в ФО-57). Документы кредита № 25-3/014 приняты 11.03.2025.</t>
+          <t>КЗ-20 ОсОО «Каракол-Сервис» (куратор Токтогулова Г. А.): нет страхового полиса на нежилое помещение по договору залога № 25-3/014-З1 от 05.03.2025; открыто задание «Истребовать страховой полис у залогодателя» от 05.08.2026, срок 19.08.2026 продлён 18.08.2026 до 20.09.2026, на 30.09.2026 в работе — как в ФО-20 (ФО-67, ФО-68 — под прежним названием «Довнести страховой полис в дело»). Отчёт об оценке от 10.03.2026 действует до 10.03.2027 (дата оценки — как в ФО-57). Документы кредита № 25-3/014 приняты 11.03.2025.</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="45" customHeight="1">
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="31" t="inlineStr">
         <is>
           <t>5.</t>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>С отбором «досье — все» в отчёт входят досье всех заёмщиков с кредитом «зарегистрирован» или «действует»; КЗ-15 и КЗ-16 (погашены), КЗ-08 (списан) и КЗ-18 (расторгнут) не входят ни при каком отборе.</t>
+          <t>С отбором «досье — все» в отчёт входят 22 досье — 25 кредитов в состоянии «зарегистрирован» или «действует»: 21 заёмщик с задолженностью (= ФО-02) и КЗ-26 (зарегистрирован 20.08.2026, освоения нет, = ФО-09). КЗ-07 — досье ОсОО «Ысык-Көл Логистик» (принял долг 09.09.2026, соглашение № 14), досье ОсОО «Эко-Продукт» не входит — кредитов на дату нет. КЗ-15 и КЗ-16 (погашены), КЗ-08 (списан 17.09.2026) и КЗ-18 (расторгнут 10.09.2026, соглашение № 5) не входят ни при каком отборе.</t>
         </is>
       </c>
     </row>
